--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepProdIndex.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepProdIndex.xlsx
@@ -126,23 +126,27 @@
     <font>
       <sz val="10.5"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -150,11 +154,13 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -197,17 +203,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -517,16 +523,16 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="9.375" customWidth="1"/>
-    <col min="3" max="3" width="15.75" style="5" customWidth="1"/>
+    <col min="3" max="3" width="15.75" style="8" customWidth="1"/>
     <col min="4" max="6" width="13.75" customWidth="1"/>
     <col min="7" max="7" width="17.5" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="6" customWidth="1"/>
-    <col min="9" max="9" width="19.375" style="6" customWidth="1"/>
+    <col min="8" max="8" width="13.75" style="5" customWidth="1"/>
+    <col min="9" max="9" width="19.375" style="5" customWidth="1"/>
     <col min="10" max="10" width="11.875" customWidth="1"/>
     <col min="11" max="13" width="13.75" customWidth="1"/>
     <col min="14" max="14" width="17.5" customWidth="1"/>
-    <col min="15" max="15" width="13.75" style="6" customWidth="1"/>
-    <col min="16" max="16" width="19.375" style="6" customWidth="1"/>
+    <col min="15" max="15" width="13.75" style="5" customWidth="1"/>
+    <col min="16" max="16" width="19.375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="24" customHeight="1">
@@ -551,10 +557,10 @@
       <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="6" t="s">
         <v>7</v>
       </c>
       <c r="J1" s="4" t="s">
@@ -572,10 +578,10 @@
       <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="P1" s="6" t="s">
         <v>14</v>
       </c>
     </row>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepProdIndex.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepProdIndex.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18525" windowHeight="7125"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18530" windowHeight="7130"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -107,7 +107,7 @@
     <t>母产品单位累计净值</t>
   </si>
   <si>
-    <t>日期(yyyy/mm/dd)*</t>
+    <t>日期(yyyy-mm-dd)*</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -209,10 +209,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -520,19 +520,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="2" width="9.375" customWidth="1"/>
-    <col min="3" max="3" width="15.75" style="8" customWidth="1"/>
-    <col min="4" max="6" width="13.75" customWidth="1"/>
-    <col min="7" max="7" width="17.5" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="5" customWidth="1"/>
-    <col min="9" max="9" width="19.375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="11.875" customWidth="1"/>
-    <col min="11" max="13" width="13.75" customWidth="1"/>
-    <col min="14" max="14" width="17.5" customWidth="1"/>
-    <col min="15" max="15" width="13.75" style="5" customWidth="1"/>
-    <col min="16" max="16" width="19.375" style="5" customWidth="1"/>
+    <col min="1" max="2" width="9.36328125" customWidth="1"/>
+    <col min="3" max="3" width="15.7265625" style="8" customWidth="1"/>
+    <col min="4" max="6" width="13.7265625" customWidth="1"/>
+    <col min="7" max="7" width="17.453125" customWidth="1"/>
+    <col min="8" max="8" width="13.7265625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="19.36328125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="11.90625" customWidth="1"/>
+    <col min="11" max="13" width="13.7265625" customWidth="1"/>
+    <col min="14" max="14" width="17.453125" customWidth="1"/>
+    <col min="15" max="15" width="13.7265625" style="5" customWidth="1"/>
+    <col min="16" max="16" width="19.36328125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="24" customHeight="1">
@@ -595,9 +595,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="16.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.6328125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
@@ -635,7 +635,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="27">
+    <row r="8" spans="1:1" ht="28">
       <c r="A8" s="4" t="s">
         <v>22</v>
       </c>
@@ -645,7 +645,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="27">
+    <row r="10" spans="1:1" ht="28">
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
@@ -670,7 +670,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="27">
+    <row r="15" spans="1:1" ht="28">
       <c r="A15" s="4" t="s">
         <v>27</v>
       </c>
@@ -680,7 +680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="27">
+    <row r="17" spans="1:1" ht="28">
       <c r="A17" s="4" t="s">
         <v>14</v>
       </c>
@@ -695,7 +695,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepProdIndex.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepProdIndex.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18530" windowHeight="7130"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18525" windowHeight="7125"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -107,7 +107,7 @@
     <t>母产品单位累计净值</t>
   </si>
   <si>
-    <t>日期(yyyy-mm-dd)*</t>
+    <t>日期(yyyy/mm/dd)*</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -520,19 +520,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="2" width="9.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.7265625" style="8" customWidth="1"/>
-    <col min="4" max="6" width="13.7265625" customWidth="1"/>
-    <col min="7" max="7" width="17.453125" customWidth="1"/>
-    <col min="8" max="8" width="13.7265625" style="5" customWidth="1"/>
-    <col min="9" max="9" width="19.36328125" style="5" customWidth="1"/>
-    <col min="10" max="10" width="11.90625" customWidth="1"/>
-    <col min="11" max="13" width="13.7265625" customWidth="1"/>
-    <col min="14" max="14" width="17.453125" customWidth="1"/>
-    <col min="15" max="15" width="13.7265625" style="5" customWidth="1"/>
-    <col min="16" max="16" width="19.36328125" style="5" customWidth="1"/>
+    <col min="1" max="2" width="9.375" customWidth="1"/>
+    <col min="3" max="3" width="15.75" style="8" customWidth="1"/>
+    <col min="4" max="6" width="13.75" customWidth="1"/>
+    <col min="7" max="7" width="17.5" customWidth="1"/>
+    <col min="8" max="8" width="13.75" style="5" customWidth="1"/>
+    <col min="9" max="9" width="19.375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="11.875" customWidth="1"/>
+    <col min="11" max="13" width="13.75" customWidth="1"/>
+    <col min="14" max="14" width="17.5" customWidth="1"/>
+    <col min="15" max="15" width="13.75" style="5" customWidth="1"/>
+    <col min="16" max="16" width="19.375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="24" customHeight="1">
@@ -595,9 +595,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="16.6328125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
@@ -635,7 +635,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="28">
+    <row r="8" spans="1:1" ht="27">
       <c r="A8" s="4" t="s">
         <v>22</v>
       </c>
@@ -645,7 +645,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="28">
+    <row r="10" spans="1:1" ht="27">
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
@@ -670,7 +670,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="28">
+    <row r="15" spans="1:1" ht="27">
       <c r="A15" s="4" t="s">
         <v>27</v>
       </c>
@@ -680,7 +680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="28">
+    <row r="17" spans="1:1" ht="27">
       <c r="A17" s="4" t="s">
         <v>14</v>
       </c>
@@ -695,7 +695,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepProdIndex.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepProdIndex.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25629"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B4D48D-F806-424C-9180-A65171BAEC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18525" windowHeight="7125"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -114,8 +115,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -209,10 +210,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -518,24 +519,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.375" customWidth="1"/>
-    <col min="3" max="3" width="15.75" style="8" customWidth="1"/>
-    <col min="4" max="6" width="13.75" customWidth="1"/>
-    <col min="7" max="7" width="17.5" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="5" customWidth="1"/>
-    <col min="9" max="9" width="19.375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="11.875" customWidth="1"/>
-    <col min="11" max="13" width="13.75" customWidth="1"/>
-    <col min="14" max="14" width="17.5" customWidth="1"/>
-    <col min="15" max="15" width="13.75" style="5" customWidth="1"/>
-    <col min="16" max="16" width="19.375" style="5" customWidth="1"/>
+    <col min="1" max="2" width="9.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" style="8" customWidth="1"/>
+    <col min="4" max="6" width="13.77734375" customWidth="1"/>
+    <col min="7" max="7" width="17.44140625" customWidth="1"/>
+    <col min="8" max="8" width="13.77734375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="19.33203125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="11.88671875" customWidth="1"/>
+    <col min="11" max="13" width="13.77734375" customWidth="1"/>
+    <col min="14" max="14" width="17.44140625" customWidth="1"/>
+    <col min="15" max="15" width="13.77734375" style="5" customWidth="1"/>
+    <col min="16" max="16" width="19.33203125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="24" customHeight="1">
+    <row r="1" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -593,94 +594,94 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="27">
+    <row r="8" spans="1:1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="27">
+    <row r="10" spans="1:1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="27">
+    <row r="15" spans="1:1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="27">
+    <row r="17" spans="1:1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>14</v>
       </c>
@@ -693,9 +694,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
